--- a/docs/StructureDefinition-mrid-launch-context.xlsx
+++ b/docs/StructureDefinition-mrid-launch-context.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mrid-launch-context.xlsx
+++ b/docs/StructureDefinition-mrid-launch-context.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mrid-launch-context.xlsx
+++ b/docs/StructureDefinition-mrid-launch-context.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mrid-launch-context.xlsx
+++ b/docs/StructureDefinition-mrid-launch-context.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="135">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/mrid-launch-context</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mrid-launch-context</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -377,7 +380,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/mrid-launch-context-name-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/mrid-launch-context-name-vs</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -405,7 +408,7 @@
     <t>Extension.extension:type.value[x]</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/mrid-launch-context-type-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/mrid-launch-context-type-vs</t>
   </si>
   <si>
     <t>Extension.extension:description</t>
@@ -687,62 +690,64 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -780,7 +785,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.72265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="75.7109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -795,123 +800,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -919,10 +924,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -934,7 +939,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -991,19 +996,19 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>20</v>
@@ -1011,10 +1016,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1022,10 +1027,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1037,13 +1042,13 @@
         <v>20</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1094,13 +1099,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1109,15 +1114,15 @@
         <v>20</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1125,10 +1130,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1140,13 +1145,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1185,31 +1190,31 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1217,26 +1222,26 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>20</v>
@@ -1245,13 +1250,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1302,19 +1307,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1322,10 +1327,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1333,10 +1338,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1348,13 +1353,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1405,13 +1410,13 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
@@ -1420,15 +1425,15 @@
         <v>20</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1436,10 +1441,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1451,13 +1456,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1496,31 +1501,31 @@
         <v>20</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -1528,10 +1533,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1539,10 +1544,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1554,16 +1559,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1571,7 +1576,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>20</v>
@@ -1613,13 +1618,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -1628,15 +1633,15 @@
         <v>20</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1644,10 +1649,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1659,13 +1664,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1692,11 +1697,11 @@
         <v>20</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y9" s="2"/>
       <c r="Z9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>20</v>
@@ -1714,46 +1719,46 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -1762,13 +1767,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1819,19 +1824,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -1839,10 +1844,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1850,10 +1855,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -1865,13 +1870,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1922,13 +1927,13 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
@@ -1937,15 +1942,15 @@
         <v>20</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1953,10 +1958,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -1968,13 +1973,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2013,31 +2018,31 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -2045,10 +2050,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2056,10 +2061,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2071,16 +2076,16 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2088,7 +2093,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -2130,13 +2135,13 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
@@ -2145,15 +2150,15 @@
         <v>20</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2161,10 +2166,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2176,13 +2181,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2209,11 +2214,11 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -2231,46 +2236,46 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
@@ -2279,13 +2284,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2336,19 +2341,19 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -2356,10 +2361,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2367,10 +2372,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -2382,13 +2387,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2439,13 +2444,13 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
@@ -2454,15 +2459,15 @@
         <v>20</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2470,10 +2475,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -2485,13 +2490,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2530,31 +2535,31 @@
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -2562,10 +2567,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2573,10 +2578,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -2588,16 +2593,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2605,7 +2610,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>20</v>
@@ -2647,13 +2652,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -2662,15 +2667,15 @@
         <v>20</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2678,10 +2683,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -2693,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2750,30 +2755,30 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2781,10 +2786,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -2796,16 +2801,16 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2855,13 +2860,13 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -2870,15 +2875,15 @@
         <v>20</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2886,10 +2891,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -2901,13 +2906,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2958,22 +2963,22 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
